--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.3446,0.1538,0.0503,0.5692</t>
-  </si>
-  <si>
-    <t>0.0133,0.0213,0.0129,0.9824</t>
-  </si>
-  <si>
-    <t>0.1838,0.1451,0.0205,0.7968</t>
-  </si>
-  <si>
-    <t>0.0213,0.3421,0.0171,0.9341</t>
-  </si>
-  <si>
-    <t>0.9909,0.0071,0.0029,0.0007</t>
-  </si>
-  <si>
-    <t>0.9884,0.0105,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.9724,0.0328,0.0069,0.0017</t>
-  </si>
-  <si>
-    <t>0.9925,0.0071,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9843,0.0180,0.0033,0.0014</t>
-  </si>
-  <si>
-    <t>0.9815,0.0221,0.0034,0.0012</t>
-  </si>
-  <si>
-    <t>0.9935,0.0053,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9897,0.0062,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.5950,0.1023,0.3691,0.0404</t>
-  </si>
-  <si>
-    <t>0.1546,0.4738,0.5531,0.0232</t>
-  </si>
-  <si>
-    <t>0.5780,0.1155,0.3823,0.0127</t>
-  </si>
-  <si>
-    <t>0.0783,0.2236,0.8016,0.0087</t>
-  </si>
-  <si>
-    <t>0.5855,0.0877,0.4134,0.0214</t>
-  </si>
-  <si>
-    <t>0.0239,0.9646,0.0265,0.0009</t>
-  </si>
-  <si>
-    <t>0.0230,0.9627,0.0329,0.0016</t>
-  </si>
-  <si>
-    <t>0.4295,0.6060,0.0339,0.0048</t>
-  </si>
-  <si>
-    <t>0.0498,0.9457,0.0167,0.0014</t>
-  </si>
-  <si>
-    <t>0.0087,0.9841,0.0146,0.0005</t>
-  </si>
-  <si>
-    <t>0.5469,0.1050,0.2501,0.1448</t>
-  </si>
-  <si>
-    <t>0.1366,0.3751,0.6608,0.0626</t>
-  </si>
-  <si>
-    <t>0.0145,0.1110,0.9540,0.0079</t>
-  </si>
-  <si>
-    <t>0.1570,0.0806,0.8035,0.0393</t>
-  </si>
-  <si>
-    <t>0.0217,0.1318,0.9315,0.0062</t>
-  </si>
-  <si>
-    <t>0.2204,0.0481,0.7990,0.0103</t>
-  </si>
-  <si>
-    <t>0.0010,0.0253,0.9928,0.0043</t>
-  </si>
-  <si>
-    <t>0.1778,0.8313,0.0278,0.0055</t>
-  </si>
-  <si>
-    <t>0.3894,0.3969,0.3327,0.0394</t>
-  </si>
-  <si>
-    <t>0.0009,0.0186,0.9930,0.0059</t>
-  </si>
-  <si>
-    <t>0.0126,0.9459,0.1652,0.0024</t>
-  </si>
-  <si>
-    <t>0.7135,0.2725,0.0575,0.0354</t>
-  </si>
-  <si>
-    <t>0.6682,0.3745,0.0350,0.0123</t>
-  </si>
-  <si>
-    <t>0.7580,0.3643,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.0365,0.9387,0.1056,0.0032</t>
-  </si>
-  <si>
-    <t>0.0093,0.9002,0.5727,0.0189</t>
-  </si>
-  <si>
-    <t>0.0062,0.2310,0.9586,0.0215</t>
-  </si>
-  <si>
-    <t>0.0052,0.7276,0.9456,0.0038</t>
-  </si>
-  <si>
-    <t>0.0264,0.1805,0.9016,0.0436</t>
-  </si>
-  <si>
-    <t>0.0089,0.3616,0.9613,0.0047</t>
-  </si>
-  <si>
-    <t>0.0008,0.9957,0.0275,0.0007</t>
-  </si>
-  <si>
-    <t>0.0051,0.7749,0.9311,0.0029</t>
-  </si>
-  <si>
-    <t>0.0298,0.4555,0.0232,0.9039</t>
-  </si>
-  <si>
-    <t>0.0090,0.9747,0.0294,0.0061</t>
-  </si>
-  <si>
-    <t>0.0024,0.9908,0.0432,0.0007</t>
-  </si>
-  <si>
-    <t>0.0014,0.9952,0.0249,0.0007</t>
-  </si>
-  <si>
-    <t>0.0046,0.6565,0.9468,0.0024</t>
-  </si>
-  <si>
-    <t>0.0023,0.8611,0.9142,0.0013</t>
-  </si>
-  <si>
-    <t>0.0335,0.1718,0.9173,0.0139</t>
-  </si>
-  <si>
-    <t>0.0263,0.1645,0.9219,0.0116</t>
-  </si>
-  <si>
-    <t>0.0011,0.0539,0.9814,0.0237</t>
-  </si>
-  <si>
-    <t>0.0080,0.1425,0.9639,0.0021</t>
-  </si>
-  <si>
-    <t>0.9617,0.0576,0.0065,0.0012</t>
-  </si>
-  <si>
-    <t>0.9536,0.0531,0.0125,0.0027</t>
-  </si>
-  <si>
-    <t>0.9828,0.0102,0.0060,0.0019</t>
-  </si>
-  <si>
-    <t>0.0066,0.0936,0.9771,0.0027</t>
-  </si>
-  <si>
-    <t>0.9845,0.0170,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.9726,0.0358,0.0030,0.0022</t>
-  </si>
-  <si>
-    <t>0.9676,0.0375,0.0081,0.0019</t>
-  </si>
-  <si>
-    <t>0.0008,0.9833,0.6061,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.3880,0.9830,0.0007</t>
-  </si>
-  <si>
-    <t>0.0062,0.1959,0.9682,0.0062</t>
-  </si>
-  <si>
-    <t>0.0003,0.9189,0.9761,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0784,0.9922,0.0021</t>
-  </si>
-  <si>
-    <t>0.0336,0.9511,0.0413,0.0025</t>
-  </si>
-  <si>
-    <t>0.0011,0.9975,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.6351,0.0372,0.3803,0.0350</t>
-  </si>
-  <si>
-    <t>0.6290,0.3328,0.0840,0.0179</t>
-  </si>
-  <si>
-    <t>0.0009,0.0288,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.0019,0.9169,0.9323,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.9756,0.7885,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9828,0.7946,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9761,0.8543,0.0004</t>
-  </si>
-  <si>
-    <t>0.0128,0.0170,0.0260,0.9776</t>
-  </si>
-  <si>
-    <t>0.0023,0.0252,0.0046,0.9946</t>
-  </si>
-  <si>
-    <t>0.0012,0.0434,0.0010,0.9969</t>
-  </si>
-  <si>
-    <t>0.0055,0.0578,0.0041,0.9908</t>
-  </si>
-  <si>
-    <t>0.0104,0.0499,0.0051,0.9868</t>
-  </si>
-  <si>
-    <t>0.0023,0.0269,0.0048,0.9944</t>
-  </si>
-  <si>
-    <t>0.0012,0.9694,0.8326,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.9795,0.8616,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.9225,0.8861,0.0018</t>
-  </si>
-  <si>
-    <t>0.0010,0.9067,0.9495,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9842,0.8964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.9071,0.8049,0.0023</t>
-  </si>
-  <si>
-    <t>0.9890,0.0097,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9809,0.0212,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.9555,0.0625,0.0098,0.0012</t>
-  </si>
-  <si>
-    <t>0.9808,0.0169,0.0055,0.0019</t>
-  </si>
-  <si>
-    <t>0.9733,0.0346,0.0048,0.0018</t>
-  </si>
-  <si>
-    <t>0.9910,0.0089,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9786,0.0267,0.0050,0.0014</t>
-  </si>
-  <si>
-    <t>0.9836,0.0185,0.0043,0.0010</t>
-  </si>
-  <si>
-    <t>0.9872,0.0112,0.0027,0.0018</t>
-  </si>
-  <si>
-    <t>0.9950,0.0032,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0055,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9922,0.0072,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9927,0.0062,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9898,0.0088,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.9928,0.0046,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9922,0.0055,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9988,0.0007</t>
-  </si>
-  <si>
-    <t>0.0462,0.2729,0.8586,0.0340</t>
-  </si>
-  <si>
-    <t>0.5960,0.0800,0.0781,0.3023</t>
-  </si>
-  <si>
-    <t>0.3055,0.0678,0.6427,0.0670</t>
-  </si>
-  <si>
-    <t>0.1183,0.9070,0.0080,0.0010</t>
-  </si>
-  <si>
-    <t>0.0529,0.9423,0.0147,0.0013</t>
-  </si>
-  <si>
-    <t>0.0675,0.9398,0.0087,0.0012</t>
-  </si>
-  <si>
-    <t>0.3921,0.7357,0.0083,0.0017</t>
-  </si>
-  <si>
-    <t>0.0364,0.9596,0.0128,0.0010</t>
-  </si>
-  <si>
-    <t>0.0096,0.9840,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.3817,0.6865,0.0185,0.0028</t>
-  </si>
-  <si>
-    <t>0.3015,0.6326,0.1456,0.0229</t>
-  </si>
-  <si>
-    <t>0.0783,0.1428,0.8146,0.0720</t>
-  </si>
-  <si>
-    <t>0.6406,0.2913,0.1112,0.0547</t>
-  </si>
-  <si>
-    <t>0.3340,0.4129,0.3314,0.1882</t>
-  </si>
-  <si>
-    <t>0.1137,0.2015,0.1025,0.8104</t>
-  </si>
-  <si>
-    <t>0.0027,0.9904,0.0430,0.0014</t>
-  </si>
-  <si>
-    <t>0.0017,0.9931,0.0373,0.0010</t>
-  </si>
-  <si>
-    <t>0.0256,0.9439,0.0483,0.0278</t>
-  </si>
-  <si>
-    <t>0.0021,0.9899,0.2280,0.0009</t>
-  </si>
-  <si>
-    <t>0.0299,0.9464,0.0956,0.0021</t>
-  </si>
-  <si>
-    <t>0.6861,0.4230,0.0134,0.0022</t>
-  </si>
-  <si>
-    <t>0.5883,0.5259,0.0126,0.0027</t>
-  </si>
-  <si>
-    <t>0.9674,0.0265,0.0146,0.0026</t>
-  </si>
-  <si>
-    <t>0.9866,0.0075,0.0036,0.0017</t>
-  </si>
-  <si>
-    <t>0.9545,0.0461,0.0115,0.0053</t>
-  </si>
-  <si>
-    <t>0.9767,0.0186,0.0091,0.0021</t>
-  </si>
-  <si>
-    <t>0.9877,0.0071,0.0026,0.0020</t>
-  </si>
-  <si>
-    <t>0.9589,0.0326,0.0137,0.0067</t>
-  </si>
-  <si>
-    <t>0.9668,0.0215,0.0187,0.0027</t>
-  </si>
-  <si>
-    <t>0.9903,0.0054,0.0028,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.8211,0.9358,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.9781,0.7121,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.7761,0.9546,0.0011</t>
-  </si>
-  <si>
-    <t>0.0057,0.7802,0.9004,0.0029</t>
-  </si>
-  <si>
-    <t>0.3664,0.5343,0.1263,0.0531</t>
-  </si>
-  <si>
-    <t>0.8540,0.0584,0.0854,0.0143</t>
-  </si>
-  <si>
-    <t>0.3749,0.0479,0.6938,0.0231</t>
-  </si>
-  <si>
-    <t>0.4477,0.4197,0.2202,0.1159</t>
-  </si>
-  <si>
-    <t>0.0259,0.0432,0.0077,0.9772</t>
-  </si>
-  <si>
-    <t>0.0004,0.0069,0.0054,0.9978</t>
-  </si>
-  <si>
-    <t>0.0008,0.0208,0.0011,0.9981</t>
-  </si>
-  <si>
-    <t>0.0087,0.0142,0.0029,0.9926</t>
-  </si>
-  <si>
-    <t>0.0013,0.9340,0.9080,0.0008</t>
-  </si>
-  <si>
-    <t>0.9768,0.0185,0.0085,0.0023</t>
-  </si>
-  <si>
-    <t>0.6633,0.3536,0.0410,0.0071</t>
-  </si>
-  <si>
-    <t>0.9694,0.0298,0.0091,0.0024</t>
-  </si>
-  <si>
-    <t>0.5920,0.5177,0.0164,0.0036</t>
-  </si>
-  <si>
-    <t>0.9866,0.0053,0.0042,0.0024</t>
-  </si>
-  <si>
-    <t>0.2020,0.1442,0.1293,0.7529</t>
-  </si>
-  <si>
-    <t>0.9798,0.0164,0.0040,0.0031</t>
-  </si>
-  <si>
-    <t>0.0187,0.1575,0.6045,0.3817</t>
-  </si>
-  <si>
-    <t>0.5814,0.0125,0.0118,0.5244</t>
-  </si>
-  <si>
-    <t>0.9517,0.0122,0.0108,0.0208</t>
-  </si>
-  <si>
-    <t>0.1999,0.7952,0.0634,0.0191</t>
-  </si>
-  <si>
-    <t>0.9046,0.0667,0.0336,0.0094</t>
-  </si>
-  <si>
-    <t>0.8997,0.1106,0.0175,0.0051</t>
-  </si>
-  <si>
-    <t>0.4596,0.5504,0.0693,0.0134</t>
-  </si>
-  <si>
-    <t>0.6707,0.3509,0.0513,0.0215</t>
-  </si>
-  <si>
-    <t>0.6637,0.2247,0.1548,0.0266</t>
-  </si>
-  <si>
-    <t>0.9912,0.0061,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9830,0.0122,0.0049,0.0021</t>
-  </si>
-  <si>
-    <t>0.9916,0.0057,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9830,0.0080,0.0036,0.0043</t>
-  </si>
-  <si>
-    <t>0.9840,0.0102,0.0032,0.0030</t>
-  </si>
-  <si>
-    <t>0.9894,0.0059,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.9920,0.0038,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9847,0.0102,0.0046,0.0021</t>
-  </si>
-  <si>
-    <t>0.1971,0.8383,0.0234,0.0038</t>
-  </si>
-  <si>
-    <t>0.7525,0.3032,0.0147,0.0018</t>
-  </si>
-  <si>
-    <t>0.5253,0.6185,0.0053,0.0011</t>
-  </si>
-  <si>
-    <t>0.3223,0.6504,0.1574,0.0213</t>
-  </si>
-  <si>
-    <t>0.8147,0.2744,0.0082,0.0011</t>
-  </si>
-  <si>
-    <t>0.9577,0.0328,0.0165,0.0050</t>
-  </si>
-  <si>
-    <t>0.9647,0.0430,0.0054,0.0022</t>
-  </si>
-  <si>
-    <t>0.8744,0.1795,0.0109,0.0024</t>
-  </si>
-  <si>
-    <t>0.0007,0.0090,0.9972,0.0011</t>
-  </si>
-  <si>
-    <t>0.9671,0.0166,0.0207,0.0021</t>
-  </si>
-  <si>
-    <t>0.0011,0.0917,0.9933,0.0010</t>
-  </si>
-  <si>
-    <t>0.0040,0.7419,0.9358,0.0026</t>
-  </si>
-  <si>
-    <t>0.0392,0.0357,0.9485,0.0097</t>
-  </si>
-  <si>
-    <t>0.0081,0.2977,0.9562,0.0023</t>
-  </si>
-  <si>
-    <t>0.0160,0.3581,0.9143,0.0058</t>
-  </si>
-  <si>
-    <t>0.0061,0.0100,0.9881,0.0023</t>
-  </si>
-  <si>
-    <t>0.0242,0.1195,0.9396,0.0096</t>
-  </si>
-  <si>
-    <t>0.1109,0.5264,0.6038,0.0478</t>
-  </si>
-  <si>
-    <t>0.1334,0.5208,0.5020,0.0378</t>
-  </si>
-  <si>
-    <t>0.4894,0.2165,0.3764,0.0434</t>
-  </si>
-  <si>
-    <t>0.3660,0.1883,0.5580,0.0211</t>
-  </si>
-  <si>
-    <t>0.1778,0.4244,0.4655,0.0141</t>
-  </si>
-  <si>
-    <t>0.1614,0.4775,0.4652,0.0159</t>
-  </si>
-  <si>
-    <t>0.5266,0.2881,0.2517,0.0601</t>
-  </si>
-  <si>
-    <t>0.3277,0.3044,0.4757,0.0604</t>
-  </si>
-  <si>
-    <t>0.7264,0.3447,0.0205,0.0024</t>
-  </si>
-  <si>
-    <t>0.5901,0.5067,0.0145,0.0028</t>
-  </si>
-  <si>
-    <t>0.5642,0.5880,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.9603,0.0686,0.0051,0.0007</t>
-  </si>
-  <si>
-    <t>0.8054,0.2614,0.0132,0.0021</t>
-  </si>
-  <si>
-    <t>0.4116,0.3759,0.2697,0.0391</t>
-  </si>
-  <si>
-    <t>0.6902,0.0359,0.3682,0.0188</t>
-  </si>
-  <si>
-    <t>0.4862,0.2071,0.3690,0.0961</t>
-  </si>
-  <si>
-    <t>0.2753,0.0765,0.5118,0.2322</t>
-  </si>
-  <si>
-    <t>0.4877,0.2953,0.1837,0.2163</t>
-  </si>
-  <si>
-    <t>0.0417,0.0604,0.9131,0.0305</t>
-  </si>
-  <si>
-    <t>0.0059,0.5245,0.9569,0.0050</t>
-  </si>
-  <si>
-    <t>0.0015,0.1564,0.9883,0.0058</t>
-  </si>
-  <si>
-    <t>0.0033,0.4796,0.9767,0.0028</t>
-  </si>
-  <si>
-    <t>0.0063,0.6990,0.9312,0.0046</t>
-  </si>
-  <si>
-    <t>0.9850,0.0141,0.0025,0.0021</t>
-  </si>
-  <si>
-    <t>0.9873,0.0141,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.9858,0.0132,0.0033,0.0014</t>
-  </si>
-  <si>
-    <t>0.9493,0.0817,0.0079,0.0014</t>
-  </si>
-  <si>
-    <t>0.9867,0.0131,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.9889,0.0124,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9846,0.0123,0.0046,0.0014</t>
-  </si>
-  <si>
-    <t>0.9841,0.0142,0.0040,0.0020</t>
-  </si>
-  <si>
-    <t>0.0712,0.2059,0.8255,0.0160</t>
-  </si>
-  <si>
-    <t>0.0568,0.8759,0.1915,0.0254</t>
-  </si>
-  <si>
-    <t>0.6713,0.1389,0.2704,0.0255</t>
-  </si>
-  <si>
-    <t>0.0073,0.0123,0.9910,0.0010</t>
-  </si>
-  <si>
-    <t>0.0006,0.0455,0.9960,0.0012</t>
-  </si>
-  <si>
-    <t>0.0154,0.7437,0.8323,0.0084</t>
-  </si>
-  <si>
-    <t>0.0004,0.0563,0.9960,0.0016</t>
-  </si>
-  <si>
-    <t>0.0802,0.4681,0.7235,0.0455</t>
-  </si>
-  <si>
-    <t>0.0001,0.0764,0.9984,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.2471,0.9871,0.0020</t>
-  </si>
-  <si>
-    <t>0.0482,0.2166,0.8725,0.0094</t>
-  </si>
-  <si>
-    <t>0.5415,0.0766,0.1254,0.3312</t>
-  </si>
-  <si>
-    <t>0.7021,0.0347,0.3045,0.0397</t>
-  </si>
-  <si>
-    <t>0.3685,0.4867,0.1528,0.2091</t>
-  </si>
-  <si>
-    <t>0.9674,0.0420,0.0092,0.0014</t>
-  </si>
-  <si>
-    <t>0.9867,0.0132,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.9887,0.0118,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9589,0.0630,0.0072,0.0012</t>
-  </si>
-  <si>
-    <t>0.9875,0.0126,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.9829,0.0181,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.9709,0.0377,0.0072,0.0016</t>
-  </si>
-  <si>
-    <t>0.9701,0.0246,0.0118,0.0026</t>
-  </si>
-  <si>
-    <t>0.0310,0.5516,0.8317,0.0157</t>
-  </si>
-  <si>
-    <t>0.0030,0.3050,0.9738,0.0056</t>
-  </si>
-  <si>
-    <t>0.0080,0.2839,0.9599,0.0039</t>
-  </si>
-  <si>
-    <t>0.0241,0.4883,0.8658,0.0078</t>
-  </si>
-  <si>
-    <t>0.0173,0.0734,0.9601,0.0076</t>
-  </si>
-  <si>
-    <t>0.0138,0.0651,0.9683,0.0087</t>
-  </si>
-  <si>
-    <t>0.0220,0.1050,0.6654,0.4158</t>
-  </si>
-  <si>
-    <t>0.0203,0.1559,0.8849,0.1022</t>
-  </si>
-  <si>
-    <t>0.7776,0.0268,0.0829,0.1219</t>
-  </si>
-  <si>
-    <t>0.0382,0.0863,0.0381,0.9536</t>
-  </si>
-  <si>
-    <t>0.0359,0.0672,0.0240,0.9589</t>
-  </si>
-  <si>
-    <t>0.0005,0.0038,0.0031,0.9982</t>
-  </si>
-  <si>
-    <t>0.0023,0.0183,0.0053,0.9948</t>
-  </si>
-  <si>
-    <t>0.4752,0.0806,0.0279,0.5596</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.5852,0.0683,0.0781,0.3124</t>
+  </si>
+  <si>
+    <t>0.0132,0.1011,0.0087,0.9775</t>
+  </si>
+  <si>
+    <t>0.4635,0.0657,0.0197,0.5563</t>
+  </si>
+  <si>
+    <t>0.0259,0.0965,0.0130,0.9669</t>
+  </si>
+  <si>
+    <t>0.9920,0.0068,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.9888,0.0143,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9881,0.0095,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0034,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9906,0.0091,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9897,0.0088,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0050,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9868,0.0083,0.0047,0.0015</t>
+  </si>
+  <si>
+    <t>0.4480,0.1944,0.4456,0.1257</t>
+  </si>
+  <si>
+    <t>0.2692,0.3670,0.5300,0.0539</t>
+  </si>
+  <si>
+    <t>0.2393,0.1403,0.6863,0.0138</t>
+  </si>
+  <si>
+    <t>0.0853,0.2082,0.8201,0.0122</t>
+  </si>
+  <si>
+    <t>0.6229,0.1444,0.2568,0.0143</t>
+  </si>
+  <si>
+    <t>0.0118,0.9823,0.0101,0.0005</t>
+  </si>
+  <si>
+    <t>0.0295,0.9582,0.0292,0.0013</t>
+  </si>
+  <si>
+    <t>0.1928,0.8294,0.0232,0.0038</t>
+  </si>
+  <si>
+    <t>0.0488,0.9349,0.0366,0.0021</t>
+  </si>
+  <si>
+    <t>0.0034,0.9925,0.0093,0.0003</t>
+  </si>
+  <si>
+    <t>0.2055,0.3504,0.5724,0.1276</t>
+  </si>
+  <si>
+    <t>0.2813,0.3737,0.3832,0.1834</t>
+  </si>
+  <si>
+    <t>0.0227,0.0404,0.9665,0.0039</t>
+  </si>
+  <si>
+    <t>0.1014,0.1582,0.8193,0.0304</t>
+  </si>
+  <si>
+    <t>0.0324,0.0528,0.9445,0.0078</t>
+  </si>
+  <si>
+    <t>0.0435,0.0267,0.9461,0.0079</t>
+  </si>
+  <si>
+    <t>0.0016,0.0121,0.9940,0.0021</t>
+  </si>
+  <si>
+    <t>0.1007,0.8535,0.0600,0.0094</t>
+  </si>
+  <si>
+    <t>0.2681,0.6664,0.1504,0.0153</t>
+  </si>
+  <si>
+    <t>0.0027,0.0796,0.9735,0.0249</t>
+  </si>
+  <si>
+    <t>0.0252,0.9420,0.0555,0.0015</t>
+  </si>
+  <si>
+    <t>0.8323,0.1576,0.0335,0.0205</t>
+  </si>
+  <si>
+    <t>0.8433,0.1480,0.0380,0.0132</t>
+  </si>
+  <si>
+    <t>0.8110,0.2785,0.0111,0.0037</t>
+  </si>
+  <si>
+    <t>0.0576,0.9347,0.0413,0.0033</t>
+  </si>
+  <si>
+    <t>0.0051,0.9500,0.4194,0.0189</t>
+  </si>
+  <si>
+    <t>0.0017,0.0912,0.9905,0.0034</t>
+  </si>
+  <si>
+    <t>0.0012,0.7157,0.9764,0.0006</t>
+  </si>
+  <si>
+    <t>0.0159,0.0901,0.9649,0.0095</t>
+  </si>
+  <si>
+    <t>0.0040,0.8369,0.9165,0.0022</t>
+  </si>
+  <si>
+    <t>0.0007,0.9961,0.0515,0.0003</t>
+  </si>
+  <si>
+    <t>0.0193,0.7559,0.8085,0.0126</t>
+  </si>
+  <si>
+    <t>0.0429,0.7316,0.0540,0.6427</t>
+  </si>
+  <si>
+    <t>0.0059,0.9808,0.0332,0.0060</t>
+  </si>
+  <si>
+    <t>0.0008,0.9969,0.0154,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9936,0.0400,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.8161,0.9741,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.7327,0.9654,0.0012</t>
+  </si>
+  <si>
+    <t>0.0265,0.0763,0.9432,0.0157</t>
+  </si>
+  <si>
+    <t>0.0326,0.0642,0.9036,0.0634</t>
+  </si>
+  <si>
+    <t>0.0012,0.1046,0.9912,0.0028</t>
+  </si>
+  <si>
+    <t>0.0182,0.4014,0.8944,0.0033</t>
+  </si>
+  <si>
+    <t>0.9712,0.0362,0.0046,0.0015</t>
+  </si>
+  <si>
+    <t>0.9846,0.0093,0.0059,0.0013</t>
+  </si>
+  <si>
+    <t>0.9040,0.1175,0.0172,0.0029</t>
+  </si>
+  <si>
+    <t>0.0080,0.0671,0.9800,0.0037</t>
+  </si>
+  <si>
+    <t>0.9808,0.0191,0.0045,0.0017</t>
+  </si>
+  <si>
+    <t>0.9746,0.0295,0.0055,0.0019</t>
+  </si>
+  <si>
+    <t>0.9552,0.0732,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.9817,0.7548,0.0009</t>
+  </si>
+  <si>
+    <t>0.0027,0.4959,0.9769,0.0016</t>
+  </si>
+  <si>
+    <t>0.0077,0.3288,0.9528,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.8797,0.9800,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.2968,0.9878,0.0014</t>
+  </si>
+  <si>
+    <t>0.0167,0.9710,0.0404,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.9967,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.4505,0.1541,0.4966,0.0254</t>
+  </si>
+  <si>
+    <t>0.7782,0.1550,0.1066,0.0242</t>
+  </si>
+  <si>
+    <t>0.0121,0.1186,0.9593,0.0073</t>
+  </si>
+  <si>
+    <t>0.0007,0.9612,0.9139,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9656,0.8221,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.9839,0.5657,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.9854,0.6867,0.0007</t>
+  </si>
+  <si>
+    <t>0.0133,0.0569,0.0110,0.9817</t>
+  </si>
+  <si>
+    <t>0.0020,0.0922,0.0030,0.9928</t>
+  </si>
+  <si>
+    <t>0.0031,0.0342,0.0020,0.9950</t>
+  </si>
+  <si>
+    <t>0.0021,0.0159,0.0019,0.9963</t>
+  </si>
+  <si>
+    <t>0.0031,0.0351,0.0071,0.9921</t>
+  </si>
+  <si>
+    <t>0.0026,0.0270,0.0053,0.9938</t>
+  </si>
+  <si>
+    <t>0.0006,0.9843,0.7707,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9401,0.9577,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.9292,0.8462,0.0017</t>
+  </si>
+  <si>
+    <t>0.0011,0.9209,0.9301,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.9755,0.8186,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.9431,0.7705,0.0019</t>
+  </si>
+  <si>
+    <t>0.9833,0.0173,0.0047,0.0012</t>
+  </si>
+  <si>
+    <t>0.9550,0.0671,0.0080,0.0013</t>
+  </si>
+  <si>
+    <t>0.9192,0.1187,0.0133,0.0017</t>
+  </si>
+  <si>
+    <t>0.9797,0.0121,0.0117,0.0010</t>
+  </si>
+  <si>
+    <t>0.9888,0.0118,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9871,0.0135,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.9851,0.0121,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.9728,0.0418,0.0050,0.0014</t>
+  </si>
+  <si>
+    <t>0.9846,0.0133,0.0035,0.0019</t>
+  </si>
+  <si>
+    <t>0.9920,0.0080,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9906,0.0084,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9905,0.0068,0.0030,0.0011</t>
+  </si>
+  <si>
+    <t>0.9934,0.0044,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9911,0.0067,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9865,0.0145,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9901,0.0079,0.0024,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0051,0.9988,0.0008</t>
+  </si>
+  <si>
+    <t>0.0236,0.1330,0.9316,0.0111</t>
+  </si>
+  <si>
+    <t>0.5521,0.1418,0.1103,0.3156</t>
+  </si>
+  <si>
+    <t>0.1060,0.0463,0.8808,0.0272</t>
+  </si>
+  <si>
+    <t>0.0509,0.9538,0.0049,0.0007</t>
+  </si>
+  <si>
+    <t>0.0913,0.9175,0.0103,0.0015</t>
+  </si>
+  <si>
+    <t>0.3364,0.7645,0.0090,0.0014</t>
+  </si>
+  <si>
+    <t>0.6032,0.4505,0.0230,0.0022</t>
+  </si>
+  <si>
+    <t>0.0346,0.9600,0.0102,0.0014</t>
+  </si>
+  <si>
+    <t>0.0179,0.9720,0.0109,0.0007</t>
+  </si>
+  <si>
+    <t>0.4745,0.5650,0.0243,0.0035</t>
+  </si>
+  <si>
+    <t>0.4906,0.3166,0.1922,0.0199</t>
+  </si>
+  <si>
+    <t>0.3191,0.0987,0.3216,0.4046</t>
+  </si>
+  <si>
+    <t>0.1256,0.7919,0.1259,0.0223</t>
+  </si>
+  <si>
+    <t>0.4735,0.2097,0.3431,0.1913</t>
+  </si>
+  <si>
+    <t>0.1533,0.4280,0.1757,0.6128</t>
+  </si>
+  <si>
+    <t>0.0018,0.9932,0.0297,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9968,0.0279,0.0003</t>
+  </si>
+  <si>
+    <t>0.0301,0.9368,0.0540,0.0187</t>
+  </si>
+  <si>
+    <t>0.0012,0.9940,0.1190,0.0005</t>
+  </si>
+  <si>
+    <t>0.0455,0.9125,0.1182,0.0034</t>
+  </si>
+  <si>
+    <t>0.7979,0.3035,0.0064,0.0013</t>
+  </si>
+  <si>
+    <t>0.5333,0.5783,0.0133,0.0021</t>
+  </si>
+  <si>
+    <t>0.9797,0.0138,0.0067,0.0023</t>
+  </si>
+  <si>
+    <t>0.9842,0.0098,0.0032,0.0030</t>
+  </si>
+  <si>
+    <t>0.9802,0.0144,0.0075,0.0019</t>
+  </si>
+  <si>
+    <t>0.9711,0.0206,0.0115,0.0035</t>
+  </si>
+  <si>
+    <t>0.9905,0.0043,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9368,0.0684,0.0145,0.0094</t>
+  </si>
+  <si>
+    <t>0.9774,0.0176,0.0059,0.0029</t>
+  </si>
+  <si>
+    <t>0.9874,0.0083,0.0029,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.9326,0.8646,0.0016</t>
+  </si>
+  <si>
+    <t>0.0033,0.9326,0.8081,0.0017</t>
+  </si>
+  <si>
+    <t>0.0045,0.5505,0.9582,0.0018</t>
+  </si>
+  <si>
+    <t>0.0058,0.8427,0.9000,0.0036</t>
+  </si>
+  <si>
+    <t>0.5259,0.2444,0.1238,0.1875</t>
+  </si>
+  <si>
+    <t>0.8103,0.0744,0.1207,0.0211</t>
+  </si>
+  <si>
+    <t>0.3221,0.0590,0.6824,0.0379</t>
+  </si>
+  <si>
+    <t>0.5481,0.2393,0.2370,0.0478</t>
+  </si>
+  <si>
+    <t>0.0430,0.0410,0.0096,0.9657</t>
+  </si>
+  <si>
+    <t>0.0004,0.0070,0.0055,0.9976</t>
+  </si>
+  <si>
+    <t>0.0022,0.0205,0.0046,0.9950</t>
+  </si>
+  <si>
+    <t>0.0103,0.0213,0.0048,0.9894</t>
+  </si>
+  <si>
+    <t>0.0006,0.9769,0.8769,0.0006</t>
+  </si>
+  <si>
+    <t>0.9768,0.0120,0.0110,0.0022</t>
+  </si>
+  <si>
+    <t>0.4580,0.5889,0.0330,0.0065</t>
+  </si>
+  <si>
+    <t>0.9641,0.0318,0.0092,0.0058</t>
+  </si>
+  <si>
+    <t>0.7620,0.3010,0.0227,0.0053</t>
+  </si>
+  <si>
+    <t>0.9813,0.0091,0.0076,0.0023</t>
+  </si>
+  <si>
+    <t>0.2548,0.1470,0.0955,0.7150</t>
+  </si>
+  <si>
+    <t>0.9703,0.0218,0.0061,0.0066</t>
+  </si>
+  <si>
+    <t>0.0524,0.1353,0.5027,0.4800</t>
+  </si>
+  <si>
+    <t>0.4838,0.0276,0.0477,0.5087</t>
+  </si>
+  <si>
+    <t>0.8589,0.0166,0.0117,0.1335</t>
+  </si>
+  <si>
+    <t>0.2183,0.7457,0.0600,0.0323</t>
+  </si>
+  <si>
+    <t>0.8390,0.1205,0.0387,0.0331</t>
+  </si>
+  <si>
+    <t>0.7098,0.2527,0.0806,0.0178</t>
+  </si>
+  <si>
+    <t>0.2412,0.7474,0.0811,0.0190</t>
+  </si>
+  <si>
+    <t>0.6300,0.2269,0.1889,0.0317</t>
+  </si>
+  <si>
+    <t>0.7192,0.1827,0.1455,0.0159</t>
+  </si>
+  <si>
+    <t>0.9895,0.0057,0.0026,0.0016</t>
+  </si>
+  <si>
+    <t>0.9864,0.0110,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.9931,0.0038,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9861,0.0067,0.0037,0.0025</t>
+  </si>
+  <si>
+    <t>0.9924,0.0038,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9898,0.0068,0.0030,0.0010</t>
+  </si>
+  <si>
+    <t>0.9898,0.0052,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9891,0.0066,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.1381,0.8885,0.0152,0.0021</t>
+  </si>
+  <si>
+    <t>0.8570,0.1974,0.0150,0.0038</t>
+  </si>
+  <si>
+    <t>0.5888,0.5487,0.0088,0.0022</t>
+  </si>
+  <si>
+    <t>0.8249,0.1500,0.0772,0.0253</t>
+  </si>
+  <si>
+    <t>0.9712,0.0430,0.0038,0.0008</t>
+  </si>
+  <si>
+    <t>0.9070,0.1079,0.0228,0.0043</t>
+  </si>
+  <si>
+    <t>0.9718,0.0302,0.0073,0.0019</t>
+  </si>
+  <si>
+    <t>0.7984,0.2832,0.0142,0.0034</t>
+  </si>
+  <si>
+    <t>0.0007,0.0051,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.9032,0.0832,0.0347,0.0025</t>
+  </si>
+  <si>
+    <t>0.0005,0.0451,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.5276,0.9755,0.0023</t>
+  </si>
+  <si>
+    <t>0.0108,0.0246,0.9744,0.0078</t>
+  </si>
+  <si>
+    <t>0.0020,0.6322,0.9636,0.0008</t>
+  </si>
+  <si>
+    <t>0.0059,0.1721,0.9727,0.0019</t>
+  </si>
+  <si>
+    <t>0.0034,0.0216,0.9916,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.4921,0.9419,0.0022</t>
+  </si>
+  <si>
+    <t>0.0496,0.2802,0.8330,0.0088</t>
+  </si>
+  <si>
+    <t>0.1107,0.6349,0.5038,0.0377</t>
+  </si>
+  <si>
+    <t>0.2979,0.3603,0.5096,0.0536</t>
+  </si>
+  <si>
+    <t>0.1150,0.6928,0.4209,0.0274</t>
+  </si>
+  <si>
+    <t>0.0457,0.8946,0.1633,0.0105</t>
+  </si>
+  <si>
+    <t>0.2329,0.4525,0.5145,0.0533</t>
+  </si>
+  <si>
+    <t>0.6383,0.1638,0.1548,0.1470</t>
+  </si>
+  <si>
+    <t>0.2160,0.5597,0.4915,0.0642</t>
+  </si>
+  <si>
+    <t>0.5991,0.4772,0.0199,0.0029</t>
+  </si>
+  <si>
+    <t>0.6948,0.3469,0.0247,0.0022</t>
+  </si>
+  <si>
+    <t>0.9083,0.1596,0.0099,0.0021</t>
+  </si>
+  <si>
+    <t>0.9825,0.0135,0.0077,0.0012</t>
+  </si>
+  <si>
+    <t>0.9665,0.0427,0.0070,0.0011</t>
+  </si>
+  <si>
+    <t>0.5124,0.2950,0.2643,0.0748</t>
+  </si>
+  <si>
+    <t>0.7320,0.0591,0.2738,0.0374</t>
+  </si>
+  <si>
+    <t>0.4935,0.2450,0.3552,0.0983</t>
+  </si>
+  <si>
+    <t>0.5429,0.0701,0.3853,0.0852</t>
+  </si>
+  <si>
+    <t>0.6967,0.1120,0.0863,0.1502</t>
+  </si>
+  <si>
+    <t>0.0116,0.0495,0.9528,0.0366</t>
+  </si>
+  <si>
+    <t>0.0031,0.5993,0.9693,0.0025</t>
+  </si>
+  <si>
+    <t>0.0027,0.4163,0.9825,0.0028</t>
+  </si>
+  <si>
+    <t>0.0165,0.1866,0.9528,0.0045</t>
+  </si>
+  <si>
+    <t>0.0038,0.6552,0.9577,0.0021</t>
+  </si>
+  <si>
+    <t>0.9846,0.0122,0.0044,0.0018</t>
+  </si>
+  <si>
+    <t>0.9922,0.0067,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9729,0.0345,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.9856,0.0163,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9882,0.0106,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.9808,0.0173,0.0061,0.0012</t>
+  </si>
+  <si>
+    <t>0.9878,0.0080,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9914,0.0052,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.0647,0.1006,0.9110,0.0067</t>
+  </si>
+  <si>
+    <t>0.1437,0.6520,0.3546,0.0230</t>
+  </si>
+  <si>
+    <t>0.8652,0.0400,0.1237,0.0165</t>
+  </si>
+  <si>
+    <t>0.0035,0.0254,0.9925,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0304,0.9946,0.0009</t>
+  </si>
+  <si>
+    <t>0.0201,0.6002,0.8027,0.0103</t>
+  </si>
+  <si>
+    <t>0.0002,0.0227,0.9975,0.0021</t>
+  </si>
+  <si>
+    <t>0.0528,0.4507,0.8273,0.0346</t>
+  </si>
+  <si>
+    <t>0.0005,0.1363,0.9953,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.1334,0.9834,0.0017</t>
+  </si>
+  <si>
+    <t>0.2130,0.4220,0.4856,0.0309</t>
+  </si>
+  <si>
+    <t>0.8256,0.0163,0.1184,0.0408</t>
+  </si>
+  <si>
+    <t>0.7145,0.0114,0.2973,0.0309</t>
+  </si>
+  <si>
+    <t>0.8100,0.0767,0.0920,0.0505</t>
+  </si>
+  <si>
+    <t>0.9591,0.0579,0.0075,0.0016</t>
+  </si>
+  <si>
+    <t>0.9880,0.0125,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.9888,0.0131,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.9725,0.0438,0.0029,0.0012</t>
+  </si>
+  <si>
+    <t>0.9843,0.0136,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.9865,0.0180,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9787,0.0207,0.0054,0.0022</t>
+  </si>
+  <si>
+    <t>0.9827,0.0181,0.0026,0.0018</t>
+  </si>
+  <si>
+    <t>0.0356,0.4439,0.8270,0.0082</t>
+  </si>
+  <si>
+    <t>0.0066,0.1259,0.9750,0.0043</t>
+  </si>
+  <si>
+    <t>0.0116,0.5265,0.9299,0.0074</t>
+  </si>
+  <si>
+    <t>0.0725,0.3913,0.7121,0.0164</t>
+  </si>
+  <si>
+    <t>0.0059,0.0180,0.9459,0.0769</t>
+  </si>
+  <si>
+    <t>0.0462,0.0491,0.9141,0.0500</t>
+  </si>
+  <si>
+    <t>0.0829,0.0402,0.9116,0.0179</t>
+  </si>
+  <si>
+    <t>0.0111,0.2923,0.9448,0.0156</t>
+  </si>
+  <si>
+    <t>0.1189,0.0769,0.1846,0.7629</t>
+  </si>
+  <si>
+    <t>0.0187,0.0594,0.0258,0.9712</t>
+  </si>
+  <si>
+    <t>0.0885,0.0950,0.0375,0.9126</t>
+  </si>
+  <si>
+    <t>0.0029,0.0153,0.0060,0.9943</t>
+  </si>
+  <si>
+    <t>0.0010,0.0329,0.0030,0.9965</t>
+  </si>
+  <si>
+    <t>0.3417,0.3640,0.0776,0.4540</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2536,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>263</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4538,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>263</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5364,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
